--- a/backend/wp_templates/D/D4 收入底稿.xlsx
+++ b/backend/wp_templates/D/D4 收入底稿.xlsx
@@ -36868,7 +36868,9 @@
       <c r="J17" s="339"/>
       <c r="K17" s="339"/>
       <c r="L17" s="339"/>
-      <c r="M17" s="339"/>
+      <c r="M17" s="339">
+        <f>SUM(C17:L17)</f>
+      </c>
       <c r="N17" s="339"/>
       <c r="O17" s="339"/>
       <c r="P17" s="345"/>
@@ -36890,7 +36892,9 @@
       <c r="J18" s="339"/>
       <c r="K18" s="339"/>
       <c r="L18" s="339"/>
-      <c r="M18" s="339"/>
+      <c r="M18" s="339">
+        <f>SUM(C18:L18)</f>
+      </c>
       <c r="N18" s="339"/>
       <c r="O18" s="339"/>
       <c r="P18" s="345"/>
@@ -36912,7 +36916,9 @@
       <c r="J19" s="339"/>
       <c r="K19" s="339"/>
       <c r="L19" s="339"/>
-      <c r="M19" s="339"/>
+      <c r="M19" s="339">
+        <f>SUM(C19:L19)</f>
+      </c>
       <c r="N19" s="339"/>
       <c r="O19" s="339"/>
       <c r="P19" s="345"/>
